--- a/Results/Results.xlsx
+++ b/Results/Results.xlsx
@@ -2,19 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="3" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Run_22-24-42" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Run_23-16-06" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Run_23-20-56" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Run_23-28-06" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Run_23-38-18" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Baseline K-fold" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pretrained" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fine-tune on Full" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fine-tune 14vs1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Fine-tune on Full1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Average Ensemble" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Average Ensemble 14 vs 1" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,11 +52,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -418,7 +421,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -705,49 +708,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44.08602150537634</v>
+        <v>48.38709677419355</v>
       </c>
       <c r="E5" t="n">
-        <v>34.40860215053764</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F5" t="n">
-        <v>98.9247311827957</v>
+        <v>96.7741935483871</v>
       </c>
       <c r="G5" t="n">
-        <v>88.17204301075269</v>
+        <v>90.32258064516128</v>
       </c>
       <c r="H5" t="n">
         <v>44.08602150537634</v>
       </c>
       <c r="I5" t="n">
-        <v>47.31182795698925</v>
+        <v>41.93548387096774</v>
       </c>
       <c r="J5" t="n">
-        <v>30.10752688172043</v>
+        <v>35.48387096774194</v>
       </c>
       <c r="K5" t="n">
+        <v>38.70967741935484</v>
+      </c>
+      <c r="L5" t="n">
+        <v>50.53763440860215</v>
+      </c>
+      <c r="M5" t="n">
+        <v>46.23655913978494</v>
+      </c>
+      <c r="N5" t="n">
         <v>39.78494623655914</v>
       </c>
-      <c r="L5" t="n">
-        <v>44.08602150537634</v>
-      </c>
-      <c r="M5" t="n">
-        <v>44.08602150537634</v>
-      </c>
-      <c r="N5" t="n">
-        <v>37.63440860215054</v>
-      </c>
       <c r="O5" t="n">
+        <v>40.86021505376344</v>
+      </c>
+      <c r="P5" t="n">
+        <v>43.01075268817204</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>43.01075268817204</v>
+      </c>
+      <c r="R5" t="n">
         <v>35.48387096774194</v>
-      </c>
-      <c r="P5" t="n">
-        <v>45.16129032258064</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>29.03225806451613</v>
-      </c>
-      <c r="R5" t="n">
-        <v>33.33333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -762,49 +765,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>56.96594427244582</v>
+        <v>75.54179566563467</v>
       </c>
       <c r="E6" t="n">
-        <v>65.01547987616098</v>
+        <v>61.91950464396285</v>
       </c>
       <c r="F6" t="n">
-        <v>95.6656346749226</v>
+        <v>92.56965944272446</v>
       </c>
       <c r="G6" t="n">
-        <v>95.97523219814241</v>
+        <v>94.73684210526315</v>
       </c>
       <c r="H6" t="n">
-        <v>68.42105263157895</v>
+        <v>68.73065015479877</v>
       </c>
       <c r="I6" t="n">
-        <v>75.85139318885449</v>
+        <v>76.78018575851394</v>
       </c>
       <c r="J6" t="n">
-        <v>52.32198142414861</v>
+        <v>54.79876160990712</v>
       </c>
       <c r="K6" t="n">
-        <v>79.25696594427245</v>
+        <v>73.37461300309597</v>
       </c>
       <c r="L6" t="n">
         <v>91.3312693498452</v>
       </c>
       <c r="M6" t="n">
+        <v>73.06501547987617</v>
+      </c>
+      <c r="N6" t="n">
+        <v>93.18885448916409</v>
+      </c>
+      <c r="O6" t="n">
         <v>79.56656346749226</v>
       </c>
-      <c r="N6" t="n">
-        <v>80.80495356037152</v>
-      </c>
-      <c r="O6" t="n">
-        <v>49.53560371517028</v>
-      </c>
       <c r="P6" t="n">
-        <v>80.80495356037152</v>
+        <v>80.18575851393189</v>
       </c>
       <c r="Q6" t="n">
-        <v>78.328173374613</v>
+        <v>77.08978328173374</v>
       </c>
       <c r="R6" t="n">
-        <v>67.49226006191951</v>
+        <v>65.3250773993808</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +822,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>43.47826086956522</v>
+        <v>41.30434782608695</v>
       </c>
       <c r="E7" t="n">
         <v>43.47826086956522</v>
       </c>
       <c r="F7" t="n">
-        <v>84.78260869565217</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="G7" t="n">
-        <v>93.47826086956522</v>
+        <v>89.13043478260869</v>
       </c>
       <c r="H7" t="n">
-        <v>36.95652173913043</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="I7" t="n">
-        <v>56.52173913043478</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
         <v>34.78260869565217</v>
@@ -846,22 +849,22 @@
         <v>56.52173913043478</v>
       </c>
       <c r="M7" t="n">
-        <v>54.34782608695652</v>
+        <v>50</v>
       </c>
       <c r="N7" t="n">
-        <v>58.69565217391305</v>
+        <v>56.52173913043478</v>
       </c>
       <c r="O7" t="n">
-        <v>41.30434782608695</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="P7" t="n">
-        <v>52.17391304347826</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="Q7" t="n">
         <v>39.1304347826087</v>
       </c>
       <c r="R7" t="n">
-        <v>47.82608695652174</v>
+        <v>45.65217391304348</v>
       </c>
     </row>
     <row r="8">
@@ -881,49 +884,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48.38709677419355</v>
+        <v>45.16129032258064</v>
       </c>
       <c r="E8" t="n">
-        <v>44.08602150537634</v>
+        <v>37.63440860215054</v>
       </c>
       <c r="F8" t="n">
-        <v>93.54838709677419</v>
+        <v>96.7741935483871</v>
       </c>
       <c r="G8" t="n">
-        <v>80.64516129032258</v>
+        <v>87.09677419354838</v>
       </c>
       <c r="H8" t="n">
-        <v>32.25806451612903</v>
+        <v>39.78494623655914</v>
       </c>
       <c r="I8" t="n">
-        <v>47.31182795698925</v>
+        <v>45.16129032258064</v>
       </c>
       <c r="J8" t="n">
         <v>41.93548387096774</v>
       </c>
       <c r="K8" t="n">
+        <v>34.40860215053764</v>
+      </c>
+      <c r="L8" t="n">
         <v>38.70967741935484</v>
       </c>
-      <c r="L8" t="n">
-        <v>48.38709677419355</v>
-      </c>
       <c r="M8" t="n">
-        <v>38.70967741935484</v>
+        <v>40.86021505376344</v>
       </c>
       <c r="N8" t="n">
-        <v>46.23655913978494</v>
+        <v>36.55913978494624</v>
       </c>
       <c r="O8" t="n">
-        <v>38.70967741935484</v>
+        <v>36.55913978494624</v>
       </c>
       <c r="P8" t="n">
-        <v>43.01075268817204</v>
+        <v>41.93548387096774</v>
       </c>
       <c r="Q8" t="n">
-        <v>35.48387096774194</v>
+        <v>36.55913978494624</v>
       </c>
       <c r="R8" t="n">
-        <v>41.93548387096774</v>
+        <v>31.18279569892473</v>
       </c>
     </row>
     <row r="9">
@@ -938,49 +941,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>92.56965944272446</v>
+        <v>90.09287925696594</v>
       </c>
       <c r="E9" t="n">
-        <v>95.35603715170279</v>
+        <v>94.11764705882352</v>
       </c>
       <c r="F9" t="n">
         <v>97.52321981424149</v>
       </c>
       <c r="G9" t="n">
-        <v>86.68730650154799</v>
+        <v>97.83281733746129</v>
       </c>
       <c r="H9" t="n">
-        <v>69.04024767801857</v>
+        <v>77.39938080495357</v>
       </c>
       <c r="I9" t="n">
-        <v>85.13931888544892</v>
+        <v>95.35603715170279</v>
       </c>
       <c r="J9" t="n">
-        <v>98.45201238390094</v>
+        <v>93.49845201238391</v>
       </c>
       <c r="K9" t="n">
-        <v>69.04024767801857</v>
+        <v>47.9876160990712</v>
       </c>
       <c r="L9" t="n">
-        <v>81.42414860681114</v>
+        <v>80.80495356037152</v>
       </c>
       <c r="M9" t="n">
-        <v>54.4891640866873</v>
+        <v>62.22910216718266</v>
       </c>
       <c r="N9" t="n">
-        <v>93.49845201238391</v>
+        <v>88.54489164086688</v>
       </c>
       <c r="O9" t="n">
-        <v>76.78018575851394</v>
+        <v>72.75541795665634</v>
       </c>
       <c r="P9" t="n">
-        <v>78.328173374613</v>
+        <v>70.89783281733746</v>
       </c>
       <c r="Q9" t="n">
-        <v>95.97523219814241</v>
+        <v>81.73374613003097</v>
       </c>
       <c r="R9" t="n">
-        <v>98.45201238390094</v>
+        <v>82.97213622291022</v>
       </c>
     </row>
     <row r="10">
@@ -995,49 +998,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58.69565217391305</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="E10" t="n">
-        <v>47.82608695652174</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="F10" t="n">
         <v>91.30434782608695</v>
       </c>
       <c r="G10" t="n">
-        <v>84.78260869565217</v>
+        <v>93.47826086956522</v>
       </c>
       <c r="H10" t="n">
-        <v>36.95652173913043</v>
+        <v>34.78260869565217</v>
       </c>
       <c r="I10" t="n">
-        <v>52.17391304347826</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="J10" t="n">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="K10" t="n">
+        <v>41.30434782608695</v>
+      </c>
+      <c r="L10" t="n">
         <v>39.1304347826087</v>
       </c>
-      <c r="K10" t="n">
-        <v>39.1304347826087</v>
-      </c>
-      <c r="L10" t="n">
-        <v>52.17391304347826</v>
-      </c>
       <c r="M10" t="n">
-        <v>32.60869565217391</v>
+        <v>41.30434782608695</v>
       </c>
       <c r="N10" t="n">
         <v>67.39130434782609</v>
       </c>
       <c r="O10" t="n">
-        <v>45.65217391304348</v>
+        <v>36.95652173913043</v>
       </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>54.34782608695652</v>
       </c>
       <c r="Q10" t="n">
-        <v>45.65217391304348</v>
+        <v>30.43478260869566</v>
       </c>
       <c r="R10" t="n">
-        <v>54.34782608695652</v>
+        <v>58.69565217391305</v>
       </c>
     </row>
     <row r="11">
@@ -1066,7 +1069,7 @@
         <v>87.09677419354838</v>
       </c>
       <c r="G11" t="n">
-        <v>87.09677419354838</v>
+        <v>88.17204301075269</v>
       </c>
       <c r="H11" t="n">
         <v>25.80645161290322</v>
@@ -1233,8 +1236,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1331,7 +1334,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DeepConvNet</t>
+          <t>CTNet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1345,49 +1348,49 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>81.44275983300373</v>
+        <v>71.21218779755365</v>
       </c>
       <c r="E2" t="n">
-        <v>82.89299055152715</v>
+        <v>87.00666520178716</v>
       </c>
       <c r="F2" t="n">
-        <v>93.56082912180473</v>
+        <v>98.48414267926464</v>
       </c>
       <c r="G2" t="n">
-        <v>89.55951073024244</v>
+        <v>98.75529187724308</v>
       </c>
       <c r="H2" t="n">
-        <v>86.41705119753901</v>
+        <v>76.02885812641911</v>
       </c>
       <c r="I2" t="n">
-        <v>91.88573939793453</v>
+        <v>85.17234307478211</v>
       </c>
       <c r="J2" t="n">
-        <v>79.65414194682488</v>
+        <v>80.61788617886178</v>
       </c>
       <c r="K2" t="n">
-        <v>75.64960082033254</v>
+        <v>78.4221782758368</v>
       </c>
       <c r="L2" t="n">
-        <v>87.44363876071193</v>
+        <v>78.13213213213213</v>
       </c>
       <c r="M2" t="n">
-        <v>79.6075587782905</v>
+        <v>77.32249322493224</v>
       </c>
       <c r="N2" t="n">
-        <v>79.37215264044532</v>
+        <v>71.9582509338607</v>
       </c>
       <c r="O2" t="n">
-        <v>79.54588735076541</v>
+        <v>64.44605581190947</v>
       </c>
       <c r="P2" t="n">
-        <v>80.45733538416465</v>
+        <v>84.08701384311141</v>
       </c>
       <c r="Q2" t="n">
-        <v>85.12268365926903</v>
+        <v>64.8711638467736</v>
       </c>
       <c r="R2" t="n">
-        <v>84.80187504577749</v>
+        <v>64.77667911814254</v>
       </c>
     </row>
     <row r="3">
@@ -1397,49 +1400,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.922186321772974</v>
+        <v>13.55286258711797</v>
       </c>
       <c r="E3" t="n">
-        <v>5.836525319688306</v>
+        <v>6.415917874078735</v>
       </c>
       <c r="F3" t="n">
-        <v>4.731839002924939</v>
+        <v>1.594093275146008</v>
       </c>
       <c r="G3" t="n">
-        <v>5.450344227195683</v>
+        <v>1.15613313871187</v>
       </c>
       <c r="H3" t="n">
-        <v>7.545017777279496</v>
+        <v>10.51800477968483</v>
       </c>
       <c r="I3" t="n">
-        <v>4.318803797289791</v>
+        <v>1.696344543651322</v>
       </c>
       <c r="J3" t="n">
-        <v>7.018658678445965</v>
+        <v>12.58344284138079</v>
       </c>
       <c r="K3" t="n">
-        <v>6.579841507741489</v>
+        <v>12.19089637817605</v>
       </c>
       <c r="L3" t="n">
-        <v>7.810155032971214</v>
+        <v>10.1217567671983</v>
       </c>
       <c r="M3" t="n">
-        <v>17.33821461703984</v>
+        <v>6.722455760674186</v>
       </c>
       <c r="N3" t="n">
-        <v>17.38065270293308</v>
+        <v>15.36162231271774</v>
       </c>
       <c r="O3" t="n">
-        <v>15.32838701269319</v>
+        <v>13.32829953059218</v>
       </c>
       <c r="P3" t="n">
-        <v>16.5538500873441</v>
+        <v>5.397192347124123</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.93191382344873</v>
+        <v>11.56969904858773</v>
       </c>
       <c r="R3" t="n">
-        <v>8.719568928294493</v>
+        <v>9.850496547653895</v>
       </c>
     </row>
     <row r="4">
@@ -1454,49 +1457,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>46.98223468910706</v>
+        <v>32.44740532959327</v>
       </c>
       <c r="E4" t="n">
-        <v>36.81159420289855</v>
+        <v>32.69284712482469</v>
       </c>
       <c r="F4" t="n">
-        <v>89.18419822346891</v>
+        <v>82.46844319775596</v>
       </c>
       <c r="G4" t="n">
-        <v>82.91023842917249</v>
+        <v>84.20991117344553</v>
       </c>
       <c r="H4" t="n">
-        <v>45.03272557269752</v>
+        <v>34.20056100981767</v>
       </c>
       <c r="I4" t="n">
-        <v>52.15988779803647</v>
+        <v>40.68022440392707</v>
       </c>
       <c r="J4" t="n">
-        <v>42.42402992052361</v>
+        <v>27.28611500701262</v>
       </c>
       <c r="K4" t="n">
-        <v>43.93408134642355</v>
+        <v>37.87050023375409</v>
       </c>
       <c r="L4" t="n">
-        <v>53.89901823281907</v>
+        <v>37.67414679756896</v>
       </c>
       <c r="M4" t="n">
-        <v>51.28564749883122</v>
+        <v>38.5273492286115</v>
       </c>
       <c r="N4" t="n">
-        <v>43.5273492286115</v>
+        <v>32.49181860682562</v>
       </c>
       <c r="O4" t="n">
-        <v>37.65778401122019</v>
+        <v>28.57643758765779</v>
       </c>
       <c r="P4" t="n">
-        <v>42.86348761103319</v>
+        <v>35.2875175315568</v>
       </c>
       <c r="Q4" t="n">
-        <v>44.15381019167836</v>
+        <v>28.15100514258999</v>
       </c>
       <c r="R4" t="n">
-        <v>44.80364656381487</v>
+        <v>33.99485741000468</v>
       </c>
     </row>
     <row r="5">
@@ -1506,56 +1509,734 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.997361719357096</v>
+        <v>8.5202465026714</v>
       </c>
       <c r="E5" t="n">
-        <v>3.440369487030416</v>
+        <v>3.46806631615597</v>
       </c>
       <c r="F5" t="n">
-        <v>6.322689950698965</v>
+        <v>3.941880003270327</v>
       </c>
       <c r="G5" t="n">
-        <v>2.435313793728297</v>
+        <v>5.061431936139021</v>
       </c>
       <c r="H5" t="n">
-        <v>3.915698493196139</v>
+        <v>4.275952095071548</v>
       </c>
       <c r="I5" t="n">
-        <v>5.040149091471211</v>
+        <v>4.689858601283316</v>
       </c>
       <c r="J5" t="n">
-        <v>2.771040133335427</v>
+        <v>5.405916999411509</v>
       </c>
       <c r="K5" t="n">
-        <v>4.29949332657658</v>
+        <v>5.072977570210232</v>
       </c>
       <c r="L5" t="n">
-        <v>5.266353602755254</v>
+        <v>6.472555800178201</v>
       </c>
       <c r="M5" t="n">
-        <v>10.759817848913</v>
+        <v>3.839140351791154</v>
       </c>
       <c r="N5" t="n">
-        <v>4.648318673552578</v>
+        <v>7.763609973250027</v>
       </c>
       <c r="O5" t="n">
-        <v>3.725478508304812</v>
+        <v>3.081327591245396</v>
       </c>
       <c r="P5" t="n">
-        <v>7.283593671257176</v>
+        <v>3.378457504081293</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.488628803730442</v>
+        <v>3.583203944345507</v>
       </c>
       <c r="R5" t="n">
-        <v>4.517370226587282</v>
+        <v>5.463191670787338</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Deep4Net</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>85.33933933933933</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75.64432725408335</v>
+      </c>
+      <c r="F6" t="n">
+        <v>96.48516809492419</v>
+      </c>
+      <c r="G6" t="n">
+        <v>95.34534534534535</v>
+      </c>
+      <c r="H6" t="n">
+        <v>65.57884713982276</v>
+      </c>
+      <c r="I6" t="n">
+        <v>78.4166117336849</v>
+      </c>
+      <c r="J6" t="n">
+        <v>58.98088332234674</v>
+      </c>
+      <c r="K6" t="n">
+        <v>66.18603969823482</v>
+      </c>
+      <c r="L6" t="n">
+        <v>85.44495715227423</v>
+      </c>
+      <c r="M6" t="n">
+        <v>72.18662565004028</v>
+      </c>
+      <c r="N6" t="n">
+        <v>74.2934153665861</v>
+      </c>
+      <c r="O6" t="n">
+        <v>74.94074562367244</v>
+      </c>
+      <c r="P6" t="n">
+        <v>70.81974657584414</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>83.33172196586831</v>
+      </c>
+      <c r="R6" t="n">
+        <v>73.69618398886692</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.775898321346224</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8.53894474514947</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.944854664257522</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.343434924255247</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10.97315911984308</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10.42064659960482</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.124540957836241</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.927021289025443</v>
+      </c>
+      <c r="L7" t="n">
+        <v>11.70183148035998</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.509546533718673</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12.56428242879971</v>
+      </c>
+      <c r="O7" t="n">
+        <v>14.61723615522784</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12.39919286804717</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8.729795990243382</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5.3159715759477</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>54.31977559607293</v>
+      </c>
+      <c r="E8" t="n">
+        <v>41.57316503038803</v>
+      </c>
+      <c r="F8" t="n">
+        <v>91.54978962131837</v>
+      </c>
+      <c r="G8" t="n">
+        <v>87.26040205703599</v>
+      </c>
+      <c r="H8" t="n">
+        <v>38.12061711079944</v>
+      </c>
+      <c r="I8" t="n">
+        <v>51.92145862552595</v>
+      </c>
+      <c r="J8" t="n">
+        <v>37.46376811594203</v>
+      </c>
+      <c r="K8" t="n">
+        <v>43.06685366993922</v>
+      </c>
+      <c r="L8" t="n">
+        <v>51.51940158952782</v>
+      </c>
+      <c r="M8" t="n">
+        <v>47.82842449742871</v>
+      </c>
+      <c r="N8" t="n">
+        <v>44.81299672744273</v>
+      </c>
+      <c r="O8" t="n">
+        <v>42.66245909303412</v>
+      </c>
+      <c r="P8" t="n">
+        <v>46.11266947171575</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>47.61337073398785</v>
+      </c>
+      <c r="R8" t="n">
+        <v>42.87050023375409</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.418813204777864</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.345716366591565</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.479168747481076</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.134305949193243</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.86623390461516</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.504475624266034</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7.298795462486767</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.829573349924428</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.098272070631584</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.35593974636413</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.268036067652654</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6.336078723364192</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.823545321897829</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.098399213094644</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.812958436977647</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DeepConvNet</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>75.0573500329598</v>
+      </c>
+      <c r="E10" t="n">
+        <v>81.80883322346736</v>
+      </c>
+      <c r="F10" t="n">
+        <v>97.45609023657805</v>
+      </c>
+      <c r="G10" t="n">
+        <v>92.91012964183696</v>
+      </c>
+      <c r="H10" t="n">
+        <v>77.20984399033179</v>
+      </c>
+      <c r="I10" t="n">
+        <v>90.57481872116018</v>
+      </c>
+      <c r="J10" t="n">
+        <v>85.1787885446422</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.49168680875998</v>
+      </c>
+      <c r="L10" t="n">
+        <v>84.20566908371786</v>
+      </c>
+      <c r="M10" t="n">
+        <v>69.63026441075222</v>
+      </c>
+      <c r="N10" t="n">
+        <v>75.26477697209404</v>
+      </c>
+      <c r="O10" t="n">
+        <v>77.48362997143485</v>
+      </c>
+      <c r="P10" t="n">
+        <v>78.03032300593277</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>82.0909690177983</v>
+      </c>
+      <c r="R10" t="n">
+        <v>79.17029224346297</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5.950738750084263</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10.13761233376331</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8848693672542154</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.256457888872887</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.872117673033427</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8.775741676239859</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.793409525491025</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.675316838215003</v>
+      </c>
+      <c r="L11" t="n">
+        <v>13.25508616255831</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11.99182052806755</v>
+      </c>
+      <c r="N11" t="n">
+        <v>11.89180655757217</v>
+      </c>
+      <c r="O11" t="n">
+        <v>10.04795482500092</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.930217647294672</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.655378848479144</v>
+      </c>
+      <c r="R11" t="n">
+        <v>17.55250582558765</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>48.69331463300608</v>
+      </c>
+      <c r="E12" t="n">
+        <v>42.85881252921926</v>
+      </c>
+      <c r="F12" t="n">
+        <v>91.35811126694716</v>
+      </c>
+      <c r="G12" t="n">
+        <v>87.02898550724639</v>
+      </c>
+      <c r="H12" t="n">
+        <v>41.99625993454885</v>
+      </c>
+      <c r="I12" t="n">
+        <v>53.47358578775128</v>
+      </c>
+      <c r="J12" t="n">
+        <v>44.14913510986442</v>
+      </c>
+      <c r="K12" t="n">
+        <v>46.34408602150538</v>
+      </c>
+      <c r="L12" t="n">
+        <v>50.64983637213651</v>
+      </c>
+      <c r="M12" t="n">
+        <v>46.33473585787751</v>
+      </c>
+      <c r="N12" t="n">
+        <v>39.83870967741935</v>
+      </c>
+      <c r="O12" t="n">
+        <v>35.08415147265077</v>
+      </c>
+      <c r="P12" t="n">
+        <v>43.73539036933146</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>42.43104254324451</v>
+      </c>
+      <c r="R12" t="n">
+        <v>41.77185600748012</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.01121883414988</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.454217583486343</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.7659488882973</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.44467529656804</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.5596258362197</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.573710455935948</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.255792224545485</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.651680140151964</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.44544480811334</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5.90854606760015</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.944738625870336</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.559359706704627</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.44615586629885</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.735909796942382</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.858020786636631</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ShallowFBCSPNet</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>80.66285797993115</v>
+      </c>
+      <c r="E14" t="n">
+        <v>78.07778510217535</v>
+      </c>
+      <c r="F14" t="n">
+        <v>95.01867721379917</v>
+      </c>
+      <c r="G14" t="n">
+        <v>98.26939134256209</v>
+      </c>
+      <c r="H14" t="n">
+        <v>74.4532337215264</v>
+      </c>
+      <c r="I14" t="n">
+        <v>80.31084743279865</v>
+      </c>
+      <c r="J14" t="n">
+        <v>65.85248663297443</v>
+      </c>
+      <c r="K14" t="n">
+        <v>77.11697062916576</v>
+      </c>
+      <c r="L14" t="n">
+        <v>92.4829707756537</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.03823335530653</v>
+      </c>
+      <c r="N14" t="n">
+        <v>68.50728777558045</v>
+      </c>
+      <c r="O14" t="n">
+        <v>69.05354134622426</v>
+      </c>
+      <c r="P14" t="n">
+        <v>88.89943602138725</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>82.19687980663592</v>
+      </c>
+      <c r="R14" t="n">
+        <v>48.60016113674651</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.77233835841765</v>
+      </c>
+      <c r="E15" t="n">
+        <v>14.99222557953135</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.260143097093526</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.251821793786997</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9.433006679833195</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.527605571993545</v>
+      </c>
+      <c r="J15" t="n">
+        <v>17.12157115411323</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9.138243623401758</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4.328978642769346</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.182487062547746</v>
+      </c>
+      <c r="N15" t="n">
+        <v>13.77071775691468</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7.38478322196538</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6.961625279356704</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>13.45987323959117</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7.391565983524959</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>38.56474988312296</v>
+      </c>
+      <c r="E16" t="n">
+        <v>35.08181393174381</v>
+      </c>
+      <c r="F16" t="n">
+        <v>85.05376344086021</v>
+      </c>
+      <c r="G16" t="n">
+        <v>83.34034595605424</v>
+      </c>
+      <c r="H16" t="n">
+        <v>34.42964001870033</v>
+      </c>
+      <c r="I16" t="n">
+        <v>45.02571294997663</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31.82328190743338</v>
+      </c>
+      <c r="K16" t="n">
+        <v>37.65778401122019</v>
+      </c>
+      <c r="L16" t="n">
+        <v>40.49088359046283</v>
+      </c>
+      <c r="M16" t="n">
+        <v>43.28190743338008</v>
+      </c>
+      <c r="N16" t="n">
+        <v>34.64001870032725</v>
+      </c>
+      <c r="O16" t="n">
+        <v>32.89387564282375</v>
+      </c>
+      <c r="P16" t="n">
+        <v>37.47545582047685</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>36.37213651238896</v>
+      </c>
+      <c r="R16" t="n">
+        <v>27.25806451612904</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7.443255148160826</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.684595275974297</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.048435753367732</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.567569233222923</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.603239145005498</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.443944581471004</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.568525503028092</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.456581663884549</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.632069551325905</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.080381036195346</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6.490675558783952</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.11712823349421</v>
+      </c>
+      <c r="P17" t="n">
+        <v>7.157085329419345</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.327569738132343</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.08441647098062</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="12">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B16:B17"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A10:A13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1567,8 +2248,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1588,75 +2269,80 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>#0</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>#1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>#2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>#3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>#4</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>#5</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>#6</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>#7</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>#8</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>#9</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>#10</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>#11</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>#12</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>#13</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>#14</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>#15</t>
         </is>
@@ -1665,231 +2351,509 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CTNet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>64.78844169246646</v>
+      </c>
+      <c r="E2" t="n">
+        <v>72.64484741264927</v>
+      </c>
+      <c r="F2" t="n">
+        <v>75.51968155683326</v>
+      </c>
+      <c r="G2" t="n">
+        <v>60.01769128704113</v>
+      </c>
+      <c r="H2" t="n">
+        <v>76.4484741264927</v>
+      </c>
+      <c r="I2" t="n">
+        <v>68.75276426360017</v>
+      </c>
+      <c r="J2" t="n">
+        <v>56.12560813799203</v>
+      </c>
+      <c r="K2" t="n">
+        <v>64.77222467934543</v>
+      </c>
+      <c r="L2" t="n">
+        <v>74.59088898717383</v>
+      </c>
+      <c r="M2" t="n">
+        <v>66.43078283945158</v>
+      </c>
+      <c r="N2" t="n">
+        <v>66.58558160106148</v>
+      </c>
+      <c r="O2" t="n">
+        <v>62.8482972136223</v>
+      </c>
+      <c r="P2" t="n">
+        <v>62.07430340557275</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>68.70853604599735</v>
+      </c>
+      <c r="R2" t="n">
+        <v>58.11587793011942</v>
+      </c>
+      <c r="S2" t="n">
+        <v>70.16806722689076</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>47.97101449275362</v>
+      </c>
+      <c r="E3" t="n">
+        <v>47.98136645962733</v>
+      </c>
+      <c r="F3" t="n">
+        <v>49.06832298136646</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40.06211180124223</v>
+      </c>
+      <c r="H3" t="n">
+        <v>44.25465838509317</v>
+      </c>
+      <c r="I3" t="n">
+        <v>44.09937888198758</v>
+      </c>
+      <c r="J3" t="n">
+        <v>43.01242236024845</v>
+      </c>
+      <c r="K3" t="n">
+        <v>44.72049689440994</v>
+      </c>
+      <c r="L3" t="n">
+        <v>50.93167701863354</v>
+      </c>
+      <c r="M3" t="n">
+        <v>43.32298136645963</v>
+      </c>
+      <c r="N3" t="n">
+        <v>46.11801242236025</v>
+      </c>
+      <c r="O3" t="n">
+        <v>43.63354037267081</v>
+      </c>
+      <c r="P3" t="n">
+        <v>43.63354037267081</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>46.27329192546583</v>
+      </c>
+      <c r="R3" t="n">
+        <v>44.40993788819875</v>
+      </c>
+      <c r="S3" t="n">
+        <v>45.80745341614907</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Deep4Net</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>54.96388028895769</v>
+      </c>
+      <c r="E4" t="n">
+        <v>67.47014595311809</v>
+      </c>
+      <c r="F4" t="n">
+        <v>60.88014153029633</v>
+      </c>
+      <c r="G4" t="n">
+        <v>63.53383458646616</v>
+      </c>
+      <c r="H4" t="n">
+        <v>61.36665192392746</v>
+      </c>
+      <c r="I4" t="n">
+        <v>56.61211853162318</v>
+      </c>
+      <c r="J4" t="n">
+        <v>62.93675364882795</v>
+      </c>
+      <c r="K4" t="n">
+        <v>54.55550641309155</v>
+      </c>
+      <c r="L4" t="n">
+        <v>65.3250773993808</v>
+      </c>
+      <c r="M4" t="n">
+        <v>57.34188412206989</v>
+      </c>
+      <c r="N4" t="n">
+        <v>68.33259619637329</v>
+      </c>
+      <c r="O4" t="n">
+        <v>58.97832817337461</v>
+      </c>
+      <c r="P4" t="n">
+        <v>59.19946926138877</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>67.60283060592658</v>
+      </c>
+      <c r="R4" t="n">
+        <v>72.60061919504643</v>
+      </c>
+      <c r="S4" t="n">
+        <v>69.77001326846528</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>48.40579710144928</v>
+      </c>
+      <c r="E5" t="n">
+        <v>53.72670807453416</v>
+      </c>
+      <c r="F5" t="n">
+        <v>52.79503105590062</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50.31055900621118</v>
+      </c>
+      <c r="H5" t="n">
+        <v>50.62111801242236</v>
+      </c>
+      <c r="I5" t="n">
+        <v>49.53416149068323</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50.31055900621118</v>
+      </c>
+      <c r="K5" t="n">
+        <v>48.75776397515528</v>
+      </c>
+      <c r="L5" t="n">
+        <v>53.2608695652174</v>
+      </c>
+      <c r="M5" t="n">
+        <v>48.91304347826087</v>
+      </c>
+      <c r="N5" t="n">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="O5" t="n">
+        <v>47.67080745341615</v>
+      </c>
+      <c r="P5" t="n">
+        <v>49.53416149068323</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>51.24223602484472</v>
+      </c>
+      <c r="R5" t="n">
+        <v>54.03726708074534</v>
+      </c>
+      <c r="S5" t="n">
+        <v>54.50310559006211</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DeepConvNet</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>63.13725490196078</v>
+      </c>
+      <c r="E6" t="n">
+        <v>59.68597965501991</v>
+      </c>
+      <c r="F6" t="n">
+        <v>60.5484298982751</v>
+      </c>
+      <c r="G6" t="n">
+        <v>58.75718708536046</v>
+      </c>
+      <c r="H6" t="n">
+        <v>59.2436974789916</v>
+      </c>
+      <c r="I6" t="n">
+        <v>59.13312693498452</v>
+      </c>
+      <c r="J6" t="n">
+        <v>61.49933657673595</v>
+      </c>
+      <c r="K6" t="n">
+        <v>65.19239274657231</v>
+      </c>
+      <c r="L6" t="n">
+        <v>61.27819548872181</v>
+      </c>
+      <c r="M6" t="n">
+        <v>53.58248562582928</v>
+      </c>
+      <c r="N6" t="n">
+        <v>61.18973905351615</v>
+      </c>
+      <c r="O6" t="n">
+        <v>63.09155241043786</v>
+      </c>
+      <c r="P6" t="n">
+        <v>61.56567890314021</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>59.88500663423264</v>
+      </c>
+      <c r="R6" t="n">
+        <v>52.12295444493586</v>
+      </c>
+      <c r="S6" t="n">
+        <v>60.76957098628925</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>51.44927536231884</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50.62111801242236</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48.75776397515528</v>
+      </c>
+      <c r="H7" t="n">
+        <v>46.11801242236025</v>
+      </c>
+      <c r="I7" t="n">
+        <v>48.4472049689441</v>
+      </c>
+      <c r="J7" t="n">
+        <v>52.48447204968944</v>
+      </c>
+      <c r="K7" t="n">
+        <v>50.46583850931678</v>
+      </c>
+      <c r="L7" t="n">
+        <v>54.19254658385093</v>
+      </c>
+      <c r="M7" t="n">
+        <v>47.51552795031056</v>
+      </c>
+      <c r="N7" t="n">
+        <v>51.08695652173913</v>
+      </c>
+      <c r="O7" t="n">
+        <v>51.70807453416148</v>
+      </c>
+      <c r="P7" t="n">
+        <v>54.03726708074534</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>51.86335403726709</v>
+      </c>
+      <c r="R7" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="S7" t="n">
+        <v>48.75776397515528</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>ShallowFBCSPNet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Train</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>avg</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>80.66285797993115</v>
-      </c>
-      <c r="E2" t="n">
-        <v>78.07778510217535</v>
-      </c>
-      <c r="F2" t="n">
-        <v>95.01867721379917</v>
-      </c>
-      <c r="G2" t="n">
-        <v>98.26939134256209</v>
-      </c>
-      <c r="H2" t="n">
-        <v>74.4532337215264</v>
-      </c>
-      <c r="I2" t="n">
-        <v>80.31084743279865</v>
-      </c>
-      <c r="J2" t="n">
-        <v>65.85248663297443</v>
-      </c>
-      <c r="K2" t="n">
-        <v>77.11697062916576</v>
-      </c>
-      <c r="L2" t="n">
-        <v>92.4829707756537</v>
-      </c>
-      <c r="M2" t="n">
-        <v>86.03823335530653</v>
-      </c>
-      <c r="N2" t="n">
-        <v>68.50728777558045</v>
-      </c>
-      <c r="O2" t="n">
-        <v>69.05354134622426</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88.89943602138725</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>82.19687980663592</v>
-      </c>
-      <c r="R2" t="n">
-        <v>48.60016113674651</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>std</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>14.77233835841765</v>
-      </c>
-      <c r="E3" t="n">
-        <v>14.99222557953135</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.260143097093526</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2.251821793786997</v>
-      </c>
-      <c r="H3" t="n">
-        <v>9.433006679833195</v>
-      </c>
-      <c r="I3" t="n">
-        <v>7.527605571993545</v>
-      </c>
-      <c r="J3" t="n">
-        <v>17.12157115411323</v>
-      </c>
-      <c r="K3" t="n">
-        <v>9.138243623401758</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4.328978642769346</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4.182487062547746</v>
-      </c>
-      <c r="N3" t="n">
-        <v>13.77071775691468</v>
-      </c>
-      <c r="O3" t="n">
-        <v>7.38478322196538</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6.961625279356704</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>13.45987323959117</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7.391565983524959</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>63.40557275541796</v>
+      </c>
+      <c r="E8" t="n">
+        <v>57.56302521008403</v>
+      </c>
+      <c r="F8" t="n">
+        <v>57.47456877487838</v>
+      </c>
+      <c r="G8" t="n">
+        <v>66.45289694825298</v>
+      </c>
+      <c r="H8" t="n">
+        <v>61.78681999115435</v>
+      </c>
+      <c r="I8" t="n">
+        <v>58.35913312693498</v>
+      </c>
+      <c r="J8" t="n">
+        <v>63.55594869526758</v>
+      </c>
+      <c r="K8" t="n">
+        <v>65.78947368421053</v>
+      </c>
+      <c r="L8" t="n">
+        <v>58.27067669172933</v>
+      </c>
+      <c r="M8" t="n">
+        <v>61.80893409995577</v>
+      </c>
+      <c r="N8" t="n">
+        <v>56.83325961963733</v>
+      </c>
+      <c r="O8" t="n">
+        <v>61.38876603272888</v>
+      </c>
+      <c r="P8" t="n">
+        <v>63.06943830163645</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>59.31003980539585</v>
+      </c>
+      <c r="R8" t="n">
+        <v>64.04245908889872</v>
+      </c>
+      <c r="S8" t="n">
+        <v>59.90712074303406</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>avg</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>38.56474988312296</v>
-      </c>
-      <c r="E4" t="n">
-        <v>35.08181393174381</v>
-      </c>
-      <c r="F4" t="n">
-        <v>85.05376344086021</v>
-      </c>
-      <c r="G4" t="n">
-        <v>83.34034595605424</v>
-      </c>
-      <c r="H4" t="n">
-        <v>34.42964001870033</v>
-      </c>
-      <c r="I4" t="n">
-        <v>45.02571294997663</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31.82328190743338</v>
-      </c>
-      <c r="K4" t="n">
-        <v>37.65778401122019</v>
-      </c>
-      <c r="L4" t="n">
-        <v>40.49088359046283</v>
-      </c>
-      <c r="M4" t="n">
-        <v>43.28190743338008</v>
-      </c>
-      <c r="N4" t="n">
-        <v>34.64001870032725</v>
-      </c>
-      <c r="O4" t="n">
-        <v>32.89387564282375</v>
-      </c>
-      <c r="P4" t="n">
-        <v>37.47545582047685</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>36.37213651238896</v>
-      </c>
-      <c r="R4" t="n">
-        <v>27.25806451612904</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>std</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>7.443255148160826</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4.684595275974297</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5.048435753367732</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.567569233222923</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.603239145005498</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.443944581471004</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.568525503028092</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.456581663884549</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4.632069551325905</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4.080381036195346</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6.490675558783952</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.11712823349421</v>
-      </c>
-      <c r="P5" t="n">
-        <v>7.157085329419345</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.327569738132343</v>
-      </c>
-      <c r="R5" t="n">
-        <v>4.08441647098062</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>47.39130434782609</v>
+      </c>
+      <c r="E9" t="n">
+        <v>43.7888198757764</v>
+      </c>
+      <c r="F9" t="n">
+        <v>43.7888198757764</v>
+      </c>
+      <c r="G9" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="H9" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="I9" t="n">
+        <v>44.40993788819875</v>
+      </c>
+      <c r="J9" t="n">
+        <v>47.36024844720497</v>
+      </c>
+      <c r="K9" t="n">
+        <v>48.13664596273292</v>
+      </c>
+      <c r="L9" t="n">
+        <v>44.40993788819875</v>
+      </c>
+      <c r="M9" t="n">
+        <v>42.70186335403726</v>
+      </c>
+      <c r="N9" t="n">
+        <v>44.09937888198758</v>
+      </c>
+      <c r="O9" t="n">
+        <v>43.63354037267081</v>
+      </c>
+      <c r="P9" t="n">
+        <v>44.25465838509317</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>44.40993788819875</v>
+      </c>
+      <c r="R9" t="n">
+        <v>45.18633540372671</v>
+      </c>
+      <c r="S9" t="n">
+        <v>43.47826086956522</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
+  <mergeCells count="4">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1901,8 +2865,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2004,110 +2968,115 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>97.52321981424149</v>
+      </c>
+      <c r="E2" t="n">
+        <v>96.59442724458205</v>
+      </c>
+      <c r="F2" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>86.37770897832817</v>
+      </c>
+      <c r="I2" t="n">
+        <v>97.21362229102168</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.75851393188854</v>
+      </c>
+      <c r="L2" t="n">
+        <v>86.9969040247678</v>
+      </c>
+      <c r="M2" t="n">
+        <v>98.14241486068111</v>
+      </c>
+      <c r="N2" t="n">
+        <v>97.52321981424149</v>
+      </c>
+      <c r="O2" t="n">
+        <v>80.49535603715169</v>
+      </c>
+      <c r="P2" t="n">
+        <v>87.92569659442725</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>84.82972136222911</v>
+      </c>
+      <c r="R2" t="n">
+        <v>83.59133126934985</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Train</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>avg</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>71.21218779755365</v>
-      </c>
-      <c r="E2" t="n">
-        <v>87.00666520178716</v>
-      </c>
-      <c r="F2" t="n">
-        <v>98.48414267926464</v>
-      </c>
-      <c r="G2" t="n">
-        <v>98.75529187724308</v>
-      </c>
-      <c r="H2" t="n">
-        <v>76.02885812641911</v>
-      </c>
-      <c r="I2" t="n">
-        <v>85.17234307478211</v>
-      </c>
-      <c r="J2" t="n">
-        <v>80.61788617886178</v>
-      </c>
-      <c r="K2" t="n">
-        <v>78.4221782758368</v>
-      </c>
-      <c r="L2" t="n">
-        <v>78.13213213213213</v>
-      </c>
-      <c r="M2" t="n">
-        <v>77.32249322493224</v>
-      </c>
-      <c r="N2" t="n">
-        <v>71.9582509338607</v>
-      </c>
-      <c r="O2" t="n">
-        <v>64.44605581190947</v>
-      </c>
-      <c r="P2" t="n">
-        <v>84.08701384311141</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>64.8711638467736</v>
-      </c>
-      <c r="R2" t="n">
-        <v>64.77667911814254</v>
-      </c>
-    </row>
-    <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>std</t>
+          <t>avg</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.55286258711797</v>
+        <v>97.52321981424149</v>
       </c>
       <c r="E3" t="n">
-        <v>6.415917874078735</v>
+        <v>96.59442724458205</v>
       </c>
       <c r="F3" t="n">
-        <v>1.594093275146008</v>
+        <v>99.69040247678018</v>
       </c>
       <c r="G3" t="n">
-        <v>1.15613313871187</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>10.51800477968483</v>
+        <v>86.37770897832817</v>
       </c>
       <c r="I3" t="n">
-        <v>1.696344543651322</v>
+        <v>97.21362229102168</v>
       </c>
       <c r="J3" t="n">
-        <v>12.58344284138079</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>12.19089637817605</v>
+        <v>85.75851393188854</v>
       </c>
       <c r="L3" t="n">
-        <v>10.1217567671983</v>
+        <v>86.9969040247678</v>
       </c>
       <c r="M3" t="n">
-        <v>6.722455760674186</v>
+        <v>98.14241486068111</v>
       </c>
       <c r="N3" t="n">
-        <v>15.36162231271774</v>
+        <v>97.52321981424149</v>
       </c>
       <c r="O3" t="n">
-        <v>13.32829953059218</v>
+        <v>80.49535603715169</v>
       </c>
       <c r="P3" t="n">
-        <v>5.397192347124123</v>
+        <v>87.92569659442725</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.56969904858773</v>
+        <v>84.82972136222911</v>
       </c>
       <c r="R3" t="n">
-        <v>9.850496547653895</v>
+        <v>83.59133126934985</v>
       </c>
     </row>
     <row r="4">
@@ -2122,108 +3091,585 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32.44740532959327</v>
+        <v>45.65217391304348</v>
       </c>
       <c r="E4" t="n">
-        <v>32.69284712482469</v>
+        <v>54.34782608695652</v>
       </c>
       <c r="F4" t="n">
-        <v>82.46844319775596</v>
+        <v>91.30434782608695</v>
       </c>
       <c r="G4" t="n">
-        <v>84.20991117344553</v>
+        <v>91.30434782608695</v>
       </c>
       <c r="H4" t="n">
-        <v>34.20056100981767</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="I4" t="n">
-        <v>40.68022440392707</v>
+        <v>54.34782608695652</v>
       </c>
       <c r="J4" t="n">
-        <v>27.28611500701262</v>
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>37.87050023375409</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="L4" t="n">
-        <v>37.67414679756896</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="M4" t="n">
-        <v>38.5273492286115</v>
+        <v>54.34782608695652</v>
       </c>
       <c r="N4" t="n">
-        <v>32.49181860682562</v>
+        <v>67.39130434782609</v>
       </c>
       <c r="O4" t="n">
-        <v>28.57643758765779</v>
+        <v>43.47826086956522</v>
       </c>
       <c r="P4" t="n">
-        <v>35.2875175315568</v>
+        <v>58.69565217391305</v>
       </c>
       <c r="Q4" t="n">
-        <v>28.15100514258999</v>
+        <v>47.82608695652174</v>
       </c>
       <c r="R4" t="n">
-        <v>33.99485741000468</v>
+        <v>45.65217391304348</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Deep4Net</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>std</t>
+          <t>avg</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8.5202465026714</v>
+        <v>78.01857585139319</v>
       </c>
       <c r="E5" t="n">
-        <v>3.46806631615597</v>
+        <v>75.54179566563467</v>
       </c>
       <c r="F5" t="n">
-        <v>3.941880003270327</v>
+        <v>99.69040247678018</v>
       </c>
       <c r="G5" t="n">
-        <v>5.061431936139021</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>4.275952095071548</v>
+        <v>85.13931888544892</v>
       </c>
       <c r="I5" t="n">
-        <v>4.689858601283316</v>
+        <v>83.90092879256966</v>
       </c>
       <c r="J5" t="n">
-        <v>5.405916999411509</v>
+        <v>81.11455108359134</v>
       </c>
       <c r="K5" t="n">
-        <v>5.072977570210232</v>
+        <v>60.99071207430341</v>
       </c>
       <c r="L5" t="n">
-        <v>6.472555800178201</v>
+        <v>86.06811145510835</v>
       </c>
       <c r="M5" t="n">
-        <v>3.839140351791154</v>
+        <v>88.54489164086688</v>
       </c>
       <c r="N5" t="n">
-        <v>7.763609973250027</v>
+        <v>70.89783281733746</v>
       </c>
       <c r="O5" t="n">
-        <v>3.081327591245396</v>
+        <v>83.59133126934985</v>
       </c>
       <c r="P5" t="n">
-        <v>3.378457504081293</v>
+        <v>78.63777089783281</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.583203944345507</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="R5" t="n">
-        <v>5.463191670787338</v>
+        <v>86.68730650154799</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>78.01857585139319</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75.54179566563467</v>
+      </c>
+      <c r="F6" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>85.13931888544892</v>
+      </c>
+      <c r="I6" t="n">
+        <v>83.90092879256966</v>
+      </c>
+      <c r="J6" t="n">
+        <v>81.11455108359134</v>
+      </c>
+      <c r="K6" t="n">
+        <v>60.99071207430341</v>
+      </c>
+      <c r="L6" t="n">
+        <v>86.06811145510835</v>
+      </c>
+      <c r="M6" t="n">
+        <v>88.54489164086688</v>
+      </c>
+      <c r="N6" t="n">
+        <v>70.89783281733746</v>
+      </c>
+      <c r="O6" t="n">
+        <v>83.59133126934985</v>
+      </c>
+      <c r="P6" t="n">
+        <v>78.63777089783281</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="R6" t="n">
+        <v>86.68730650154799</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="F7" t="n">
+        <v>93.47826086956522</v>
+      </c>
+      <c r="G7" t="n">
+        <v>95.65217391304348</v>
+      </c>
+      <c r="H7" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="I7" t="n">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="J7" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="K7" t="n">
+        <v>36.95652173913043</v>
+      </c>
+      <c r="L7" t="n">
+        <v>71.73913043478261</v>
+      </c>
+      <c r="M7" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="N7" t="n">
+        <v>67.39130434782609</v>
+      </c>
+      <c r="O7" t="n">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="P7" t="n">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="R7" t="n">
+        <v>58.69565217391305</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DeepConvNet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>88.54489164086688</v>
+      </c>
+      <c r="E8" t="n">
+        <v>82.97213622291022</v>
+      </c>
+      <c r="F8" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="G8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="n">
+        <v>94.11764705882352</v>
+      </c>
+      <c r="I8" t="n">
+        <v>99.38080495356037</v>
+      </c>
+      <c r="J8" t="n">
+        <v>88.54489164086688</v>
+      </c>
+      <c r="K8" t="n">
+        <v>95.35603715170279</v>
+      </c>
+      <c r="L8" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="M8" t="n">
+        <v>92.26006191950464</v>
+      </c>
+      <c r="N8" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="O8" t="n">
+        <v>92.26006191950464</v>
+      </c>
+      <c r="P8" t="n">
+        <v>83.28173374613003</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>97.83281733746129</v>
+      </c>
+      <c r="R8" t="n">
+        <v>89.16408668730649</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>88.54489164086688</v>
+      </c>
+      <c r="E9" t="n">
+        <v>82.97213622291022</v>
+      </c>
+      <c r="F9" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>94.11764705882352</v>
+      </c>
+      <c r="I9" t="n">
+        <v>99.38080495356037</v>
+      </c>
+      <c r="J9" t="n">
+        <v>88.54489164086688</v>
+      </c>
+      <c r="K9" t="n">
+        <v>95.35603715170279</v>
+      </c>
+      <c r="L9" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="M9" t="n">
+        <v>92.26006191950464</v>
+      </c>
+      <c r="N9" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="O9" t="n">
+        <v>92.26006191950464</v>
+      </c>
+      <c r="P9" t="n">
+        <v>83.28173374613003</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>97.83281733746129</v>
+      </c>
+      <c r="R9" t="n">
+        <v>89.16408668730649</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="F10" t="n">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="G10" t="n">
+        <v>97.82608695652173</v>
+      </c>
+      <c r="H10" t="n">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="I10" t="n">
+        <v>73.91304347826086</v>
+      </c>
+      <c r="J10" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="K10" t="n">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="L10" t="n">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="M10" t="n">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="N10" t="n">
+        <v>71.73913043478261</v>
+      </c>
+      <c r="O10" t="n">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="P10" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>67.39130434782609</v>
+      </c>
+      <c r="R10" t="n">
+        <v>54.34782608695652</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ShallowFBCSPNet</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="E11" t="n">
+        <v>93.80804953560371</v>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" t="n">
+        <v>98.45201238390094</v>
+      </c>
+      <c r="H11" t="n">
+        <v>78.63777089783281</v>
+      </c>
+      <c r="I11" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="J11" t="n">
+        <v>94.73684210526315</v>
+      </c>
+      <c r="K11" t="n">
+        <v>82.35294117647058</v>
+      </c>
+      <c r="L11" t="n">
+        <v>80.18575851393189</v>
+      </c>
+      <c r="M11" t="n">
+        <v>88.23529411764706</v>
+      </c>
+      <c r="N11" t="n">
+        <v>89.16408668730649</v>
+      </c>
+      <c r="O11" t="n">
+        <v>75.23219814241486</v>
+      </c>
+      <c r="P11" t="n">
+        <v>97.83281733746129</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>96.59442724458205</v>
+      </c>
+      <c r="R11" t="n">
+        <v>91.3312693498452</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="E12" t="n">
+        <v>93.80804953560371</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>98.45201238390094</v>
+      </c>
+      <c r="H12" t="n">
+        <v>78.63777089783281</v>
+      </c>
+      <c r="I12" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="J12" t="n">
+        <v>94.73684210526315</v>
+      </c>
+      <c r="K12" t="n">
+        <v>82.35294117647058</v>
+      </c>
+      <c r="L12" t="n">
+        <v>80.18575851393189</v>
+      </c>
+      <c r="M12" t="n">
+        <v>88.23529411764706</v>
+      </c>
+      <c r="N12" t="n">
+        <v>89.16408668730649</v>
+      </c>
+      <c r="O12" t="n">
+        <v>75.23219814241486</v>
+      </c>
+      <c r="P12" t="n">
+        <v>97.83281733746129</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>96.59442724458205</v>
+      </c>
+      <c r="R12" t="n">
+        <v>91.3312693498452</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>67.39130434782609</v>
+      </c>
+      <c r="E13" t="n">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="F13" t="n">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="G13" t="n">
+        <v>89.13043478260869</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="J13" t="n">
+        <v>50</v>
+      </c>
+      <c r="K13" t="n">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="L13" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="M13" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="N13" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="O13" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="P13" t="n">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="R13" t="n">
+        <v>45.65217391304348</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
+  <mergeCells count="4">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A8:A10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2235,7 +3681,1924 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>#14</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>#15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CTNet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>32.25806451612903</v>
+      </c>
+      <c r="E2" t="n">
+        <v>39.78494623655914</v>
+      </c>
+      <c r="F2" t="n">
+        <v>84.94623655913979</v>
+      </c>
+      <c r="G2" t="n">
+        <v>87.09677419354838</v>
+      </c>
+      <c r="H2" t="n">
+        <v>44.08602150537634</v>
+      </c>
+      <c r="I2" t="n">
+        <v>40.86021505376344</v>
+      </c>
+      <c r="J2" t="n">
+        <v>52.68817204301075</v>
+      </c>
+      <c r="K2" t="n">
+        <v>46.23655913978494</v>
+      </c>
+      <c r="L2" t="n">
+        <v>40.86021505376344</v>
+      </c>
+      <c r="M2" t="n">
+        <v>54.83870967741935</v>
+      </c>
+      <c r="N2" t="n">
+        <v>39.78494623655914</v>
+      </c>
+      <c r="O2" t="n">
+        <v>49.46236559139785</v>
+      </c>
+      <c r="P2" t="n">
+        <v>50.53763440860215</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>41.93548387096774</v>
+      </c>
+      <c r="R2" t="n">
+        <v>44.08602150537634</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>58.51393188854489</v>
+      </c>
+      <c r="E3" t="n">
+        <v>65.01547987616098</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="H3" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="I3" t="n">
+        <v>69.04024767801857</v>
+      </c>
+      <c r="J3" t="n">
+        <v>81.73374613003097</v>
+      </c>
+      <c r="K3" t="n">
+        <v>60.37151702786377</v>
+      </c>
+      <c r="L3" t="n">
+        <v>68.73065015479877</v>
+      </c>
+      <c r="M3" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="N3" t="n">
+        <v>78.94736842105263</v>
+      </c>
+      <c r="O3" t="n">
+        <v>57.89473684210527</v>
+      </c>
+      <c r="P3" t="n">
+        <v>93.80804953560371</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>63.77708978328174</v>
+      </c>
+      <c r="R3" t="n">
+        <v>83.90092879256966</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>32.60869565217391</v>
+      </c>
+      <c r="E4" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="F4" t="n">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="G4" t="n">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="H4" t="n">
+        <v>36.95652173913043</v>
+      </c>
+      <c r="I4" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="J4" t="n">
+        <v>41.30434782608695</v>
+      </c>
+      <c r="K4" t="n">
+        <v>41.30434782608695</v>
+      </c>
+      <c r="L4" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="M4" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="N4" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="O4" t="n">
+        <v>28.26086956521739</v>
+      </c>
+      <c r="P4" t="n">
+        <v>41.30434782608695</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>41.30434782608695</v>
+      </c>
+      <c r="R4" t="n">
+        <v>36.95652173913043</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Deep4Net</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>50.53763440860215</v>
+      </c>
+      <c r="E5" t="n">
+        <v>43.01075268817204</v>
+      </c>
+      <c r="F5" t="n">
+        <v>89.24731182795699</v>
+      </c>
+      <c r="G5" t="n">
+        <v>92.47311827956989</v>
+      </c>
+      <c r="H5" t="n">
+        <v>38.70967741935484</v>
+      </c>
+      <c r="I5" t="n">
+        <v>63.44086021505376</v>
+      </c>
+      <c r="J5" t="n">
+        <v>48.38709677419355</v>
+      </c>
+      <c r="K5" t="n">
+        <v>47.31182795698925</v>
+      </c>
+      <c r="L5" t="n">
+        <v>51.61290322580645</v>
+      </c>
+      <c r="M5" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="N5" t="n">
+        <v>43.01075268817204</v>
+      </c>
+      <c r="O5" t="n">
+        <v>51.61290322580645</v>
+      </c>
+      <c r="P5" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>59.13978494623656</v>
+      </c>
+      <c r="R5" t="n">
+        <v>46.23655913978494</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>68.73065015479877</v>
+      </c>
+      <c r="E6" t="n">
+        <v>69.04024767801857</v>
+      </c>
+      <c r="F6" t="n">
+        <v>99.07120743034056</v>
+      </c>
+      <c r="G6" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="H6" t="n">
+        <v>68.11145510835914</v>
+      </c>
+      <c r="I6" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="J6" t="n">
+        <v>92.26006191950464</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.75851393188854</v>
+      </c>
+      <c r="L6" t="n">
+        <v>87.92569659442725</v>
+      </c>
+      <c r="M6" t="n">
+        <v>68.11145510835914</v>
+      </c>
+      <c r="N6" t="n">
+        <v>86.68730650154799</v>
+      </c>
+      <c r="O6" t="n">
+        <v>95.97523219814241</v>
+      </c>
+      <c r="P6" t="n">
+        <v>66.56346749226006</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>87.61609907120743</v>
+      </c>
+      <c r="R6" t="n">
+        <v>62.8482972136223</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="E7" t="n">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="F7" t="n">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="G7" t="n">
+        <v>95.65217391304348</v>
+      </c>
+      <c r="H7" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="I7" t="n">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="J7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K7" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="L7" t="n">
+        <v>71.73913043478261</v>
+      </c>
+      <c r="M7" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="N7" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="O7" t="n">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="P7" t="n">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="R7" t="n">
+        <v>56.52173913043478</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DeepConvNet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>48.38709677419355</v>
+      </c>
+      <c r="E8" t="n">
+        <v>45.16129032258064</v>
+      </c>
+      <c r="F8" t="n">
+        <v>89.24731182795699</v>
+      </c>
+      <c r="G8" t="n">
+        <v>91.39784946236558</v>
+      </c>
+      <c r="H8" t="n">
+        <v>47.31182795698925</v>
+      </c>
+      <c r="I8" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="J8" t="n">
+        <v>51.61290322580645</v>
+      </c>
+      <c r="K8" t="n">
+        <v>44.08602150537634</v>
+      </c>
+      <c r="L8" t="n">
+        <v>56.98924731182796</v>
+      </c>
+      <c r="M8" t="n">
+        <v>51.61290322580645</v>
+      </c>
+      <c r="N8" t="n">
+        <v>39.78494623655914</v>
+      </c>
+      <c r="O8" t="n">
+        <v>49.46236559139785</v>
+      </c>
+      <c r="P8" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>47.31182795698925</v>
+      </c>
+      <c r="R8" t="n">
+        <v>45.16129032258064</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>68.42105263157895</v>
+      </c>
+      <c r="E9" t="n">
+        <v>77.08978328173374</v>
+      </c>
+      <c r="F9" t="n">
+        <v>95.35603715170279</v>
+      </c>
+      <c r="G9" t="n">
+        <v>98.76160990712074</v>
+      </c>
+      <c r="H9" t="n">
+        <v>69.96904024767801</v>
+      </c>
+      <c r="I9" t="n">
+        <v>82.97213622291022</v>
+      </c>
+      <c r="J9" t="n">
+        <v>89.78328173374614</v>
+      </c>
+      <c r="K9" t="n">
+        <v>83.59133126934985</v>
+      </c>
+      <c r="L9" t="n">
+        <v>84.52012383900929</v>
+      </c>
+      <c r="M9" t="n">
+        <v>83.59133126934985</v>
+      </c>
+      <c r="N9" t="n">
+        <v>90.71207430340557</v>
+      </c>
+      <c r="O9" t="n">
+        <v>65.01547987616098</v>
+      </c>
+      <c r="P9" t="n">
+        <v>79.56656346749226</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>90.40247678018576</v>
+      </c>
+      <c r="R9" t="n">
+        <v>64.39628482972137</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="E10" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="F10" t="n">
+        <v>89.13043478260869</v>
+      </c>
+      <c r="G10" t="n">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="H10" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="I10" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="J10" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="K10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L10" t="n">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="M10" t="n">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="N10" t="n">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="O10" t="n">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="P10" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="R10" t="n">
+        <v>52.17391304347826</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ShallowFBCSPNet</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>37.63440860215054</v>
+      </c>
+      <c r="E11" t="n">
+        <v>39.78494623655914</v>
+      </c>
+      <c r="F11" t="n">
+        <v>84.94623655913979</v>
+      </c>
+      <c r="G11" t="n">
+        <v>83.87096774193549</v>
+      </c>
+      <c r="H11" t="n">
+        <v>45.16129032258064</v>
+      </c>
+      <c r="I11" t="n">
+        <v>59.13978494623656</v>
+      </c>
+      <c r="J11" t="n">
+        <v>47.31182795698925</v>
+      </c>
+      <c r="K11" t="n">
+        <v>39.78494623655914</v>
+      </c>
+      <c r="L11" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="M11" t="n">
+        <v>50.53763440860215</v>
+      </c>
+      <c r="N11" t="n">
+        <v>45.16129032258064</v>
+      </c>
+      <c r="O11" t="n">
+        <v>35.48387096774194</v>
+      </c>
+      <c r="P11" t="n">
+        <v>48.38709677419355</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>38.70967741935484</v>
+      </c>
+      <c r="R11" t="n">
+        <v>43.01075268817204</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>74.30340557275542</v>
+      </c>
+      <c r="E12" t="n">
+        <v>76.78018575851394</v>
+      </c>
+      <c r="F12" t="n">
+        <v>98.45201238390094</v>
+      </c>
+      <c r="G12" t="n">
+        <v>94.73684210526315</v>
+      </c>
+      <c r="H12" t="n">
+        <v>75.54179566563467</v>
+      </c>
+      <c r="I12" t="n">
+        <v>83.28173374613003</v>
+      </c>
+      <c r="J12" t="n">
+        <v>85.13931888544892</v>
+      </c>
+      <c r="K12" t="n">
+        <v>80.18575851393189</v>
+      </c>
+      <c r="L12" t="n">
+        <v>78.63777089783281</v>
+      </c>
+      <c r="M12" t="n">
+        <v>96.59442724458205</v>
+      </c>
+      <c r="N12" t="n">
+        <v>89.16408668730649</v>
+      </c>
+      <c r="O12" t="n">
+        <v>75.85139318885449</v>
+      </c>
+      <c r="P12" t="n">
+        <v>95.6656346749226</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>69.04024767801857</v>
+      </c>
+      <c r="R12" t="n">
+        <v>89.47368421052632</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="E13" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="F13" t="n">
+        <v>86.95652173913044</v>
+      </c>
+      <c r="G13" t="n">
+        <v>82.60869565217391</v>
+      </c>
+      <c r="H13" t="n">
+        <v>39.1304347826087</v>
+      </c>
+      <c r="I13" t="n">
+        <v>41.30434782608695</v>
+      </c>
+      <c r="J13" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="K13" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="L13" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="M13" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="N13" t="n">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="O13" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="P13" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>30.43478260869566</v>
+      </c>
+      <c r="R13" t="n">
+        <v>54.34782608695652</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A8:A10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>#14</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>#15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CTNet</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>46.23655913978494</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44.08602150537634</v>
+      </c>
+      <c r="F2" t="n">
+        <v>88.17204301075269</v>
+      </c>
+      <c r="G2" t="n">
+        <v>90.32258064516128</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40.86021505376344</v>
+      </c>
+      <c r="I2" t="n">
+        <v>50.53763440860215</v>
+      </c>
+      <c r="J2" t="n">
+        <v>46.23655913978494</v>
+      </c>
+      <c r="K2" t="n">
+        <v>47.31182795698925</v>
+      </c>
+      <c r="L2" t="n">
+        <v>46.23655913978494</v>
+      </c>
+      <c r="M2" t="n">
+        <v>54.83870967741935</v>
+      </c>
+      <c r="N2" t="n">
+        <v>43.01075268817204</v>
+      </c>
+      <c r="O2" t="n">
+        <v>50.53763440860215</v>
+      </c>
+      <c r="P2" t="n">
+        <v>47.31182795698925</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>38.70967741935484</v>
+      </c>
+      <c r="R2" t="n">
+        <v>45.16129032258064</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>97.52321981424149</v>
+      </c>
+      <c r="E3" t="n">
+        <v>96.59442724458205</v>
+      </c>
+      <c r="F3" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="n">
+        <v>86.37770897832817</v>
+      </c>
+      <c r="I3" t="n">
+        <v>97.21362229102168</v>
+      </c>
+      <c r="J3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.75851393188854</v>
+      </c>
+      <c r="L3" t="n">
+        <v>86.9969040247678</v>
+      </c>
+      <c r="M3" t="n">
+        <v>98.14241486068111</v>
+      </c>
+      <c r="N3" t="n">
+        <v>97.52321981424149</v>
+      </c>
+      <c r="O3" t="n">
+        <v>80.49535603715169</v>
+      </c>
+      <c r="P3" t="n">
+        <v>87.92569659442725</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>84.82972136222911</v>
+      </c>
+      <c r="R3" t="n">
+        <v>83.59133126934985</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="E4" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="F4" t="n">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="G4" t="n">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="H4" t="n">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="I4" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="L4" t="n">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="M4" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="N4" t="n">
+        <v>67.39130434782609</v>
+      </c>
+      <c r="O4" t="n">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="P4" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="R4" t="n">
+        <v>45.65217391304348</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Deep4Net</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>51.61290322580645</v>
+      </c>
+      <c r="E5" t="n">
+        <v>49.46236559139785</v>
+      </c>
+      <c r="F5" t="n">
+        <v>92.47311827956989</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93.54838709677419</v>
+      </c>
+      <c r="H5" t="n">
+        <v>62.36559139784946</v>
+      </c>
+      <c r="I5" t="n">
+        <v>60.21505376344086</v>
+      </c>
+      <c r="J5" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="K5" t="n">
+        <v>36.55913978494624</v>
+      </c>
+      <c r="L5" t="n">
+        <v>56.98924731182796</v>
+      </c>
+      <c r="M5" t="n">
+        <v>60.21505376344086</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.23655913978494</v>
+      </c>
+      <c r="O5" t="n">
+        <v>62.36559139784946</v>
+      </c>
+      <c r="P5" t="n">
+        <v>54.83870967741935</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="R5" t="n">
+        <v>44.08602150537634</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>78.01857585139319</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75.54179566563467</v>
+      </c>
+      <c r="F6" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>85.13931888544892</v>
+      </c>
+      <c r="I6" t="n">
+        <v>83.90092879256966</v>
+      </c>
+      <c r="J6" t="n">
+        <v>81.11455108359134</v>
+      </c>
+      <c r="K6" t="n">
+        <v>60.99071207430341</v>
+      </c>
+      <c r="L6" t="n">
+        <v>86.06811145510835</v>
+      </c>
+      <c r="M6" t="n">
+        <v>88.54489164086688</v>
+      </c>
+      <c r="N6" t="n">
+        <v>70.89783281733746</v>
+      </c>
+      <c r="O6" t="n">
+        <v>83.59133126934985</v>
+      </c>
+      <c r="P6" t="n">
+        <v>78.63777089783281</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>89.47368421052632</v>
+      </c>
+      <c r="R6" t="n">
+        <v>86.68730650154799</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="F7" t="n">
+        <v>93.47826086956522</v>
+      </c>
+      <c r="G7" t="n">
+        <v>95.65217391304348</v>
+      </c>
+      <c r="H7" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="I7" t="n">
+        <v>63.04347826086957</v>
+      </c>
+      <c r="J7" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="K7" t="n">
+        <v>36.95652173913043</v>
+      </c>
+      <c r="L7" t="n">
+        <v>71.73913043478261</v>
+      </c>
+      <c r="M7" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="N7" t="n">
+        <v>67.39130434782609</v>
+      </c>
+      <c r="O7" t="n">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="P7" t="n">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="R7" t="n">
+        <v>58.69565217391305</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DeepConvNet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>56.98924731182796</v>
+      </c>
+      <c r="E8" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="F8" t="n">
+        <v>93.54838709677419</v>
+      </c>
+      <c r="G8" t="n">
+        <v>92.47311827956989</v>
+      </c>
+      <c r="H8" t="n">
+        <v>55.91397849462365</v>
+      </c>
+      <c r="I8" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="J8" t="n">
+        <v>56.98924731182796</v>
+      </c>
+      <c r="K8" t="n">
+        <v>46.23655913978494</v>
+      </c>
+      <c r="L8" t="n">
+        <v>62.36559139784946</v>
+      </c>
+      <c r="M8" t="n">
+        <v>61.29032258064516</v>
+      </c>
+      <c r="N8" t="n">
+        <v>49.46236559139785</v>
+      </c>
+      <c r="O8" t="n">
+        <v>48.38709677419355</v>
+      </c>
+      <c r="P8" t="n">
+        <v>58.06451612903226</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>58.06451612903226</v>
+      </c>
+      <c r="R8" t="n">
+        <v>48.38709677419355</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>88.54489164086688</v>
+      </c>
+      <c r="E9" t="n">
+        <v>82.97213622291022</v>
+      </c>
+      <c r="F9" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>94.11764705882352</v>
+      </c>
+      <c r="I9" t="n">
+        <v>99.38080495356037</v>
+      </c>
+      <c r="J9" t="n">
+        <v>88.54489164086688</v>
+      </c>
+      <c r="K9" t="n">
+        <v>95.35603715170279</v>
+      </c>
+      <c r="L9" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="M9" t="n">
+        <v>92.26006191950464</v>
+      </c>
+      <c r="N9" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="O9" t="n">
+        <v>92.26006191950464</v>
+      </c>
+      <c r="P9" t="n">
+        <v>83.28173374613003</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>97.83281733746129</v>
+      </c>
+      <c r="R9" t="n">
+        <v>89.16408668730649</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="F10" t="n">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="G10" t="n">
+        <v>97.82608695652173</v>
+      </c>
+      <c r="H10" t="n">
+        <v>52.17391304347826</v>
+      </c>
+      <c r="I10" t="n">
+        <v>73.91304347826086</v>
+      </c>
+      <c r="J10" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="K10" t="n">
+        <v>60.86956521739131</v>
+      </c>
+      <c r="L10" t="n">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="M10" t="n">
+        <v>65.21739130434783</v>
+      </c>
+      <c r="N10" t="n">
+        <v>71.73913043478261</v>
+      </c>
+      <c r="O10" t="n">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="P10" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>67.39130434782609</v>
+      </c>
+      <c r="R10" t="n">
+        <v>54.34782608695652</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ShallowFBCSPNet</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>48.38709677419355</v>
+      </c>
+      <c r="E11" t="n">
+        <v>48.38709677419355</v>
+      </c>
+      <c r="F11" t="n">
+        <v>88.17204301075269</v>
+      </c>
+      <c r="G11" t="n">
+        <v>90.32258064516128</v>
+      </c>
+      <c r="H11" t="n">
+        <v>50.53763440860215</v>
+      </c>
+      <c r="I11" t="n">
+        <v>52.68817204301075</v>
+      </c>
+      <c r="J11" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="K11" t="n">
+        <v>41.93548387096774</v>
+      </c>
+      <c r="L11" t="n">
+        <v>52.68817204301075</v>
+      </c>
+      <c r="M11" t="n">
+        <v>54.83870967741935</v>
+      </c>
+      <c r="N11" t="n">
+        <v>45.16129032258064</v>
+      </c>
+      <c r="O11" t="n">
+        <v>53.76344086021505</v>
+      </c>
+      <c r="P11" t="n">
+        <v>56.98924731182796</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>45.16129032258064</v>
+      </c>
+      <c r="R11" t="n">
+        <v>36.55913978494624</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>99.69040247678018</v>
+      </c>
+      <c r="E12" t="n">
+        <v>93.80804953560371</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>98.45201238390094</v>
+      </c>
+      <c r="H12" t="n">
+        <v>78.63777089783281</v>
+      </c>
+      <c r="I12" t="n">
+        <v>91.95046439628483</v>
+      </c>
+      <c r="J12" t="n">
+        <v>94.73684210526315</v>
+      </c>
+      <c r="K12" t="n">
+        <v>82.35294117647058</v>
+      </c>
+      <c r="L12" t="n">
+        <v>80.18575851393189</v>
+      </c>
+      <c r="M12" t="n">
+        <v>88.23529411764706</v>
+      </c>
+      <c r="N12" t="n">
+        <v>89.16408668730649</v>
+      </c>
+      <c r="O12" t="n">
+        <v>75.23219814241486</v>
+      </c>
+      <c r="P12" t="n">
+        <v>97.83281733746129</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>96.59442724458205</v>
+      </c>
+      <c r="R12" t="n">
+        <v>91.3312693498452</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>67.39130434782609</v>
+      </c>
+      <c r="E13" t="n">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="F13" t="n">
+        <v>91.30434782608695</v>
+      </c>
+      <c r="G13" t="n">
+        <v>89.13043478260869</v>
+      </c>
+      <c r="H13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I13" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="J13" t="n">
+        <v>50</v>
+      </c>
+      <c r="K13" t="n">
+        <v>43.47826086956522</v>
+      </c>
+      <c r="L13" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="M13" t="n">
+        <v>58.69565217391305</v>
+      </c>
+      <c r="N13" t="n">
+        <v>54.34782608695652</v>
+      </c>
+      <c r="O13" t="n">
+        <v>45.65217391304348</v>
+      </c>
+      <c r="P13" t="n">
+        <v>56.52173913043478</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>47.82608695652174</v>
+      </c>
+      <c r="R13" t="n">
+        <v>45.65217391304348</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A8:A10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>#11</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>#12</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>#13</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>#14</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>#15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Avg Ensmble</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6021505376344086</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5698924731182796</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.946236559139785</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.946236559139785</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5698924731182796</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6881720430107527</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5268817204301075</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6559139784946236</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6559139784946236</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.5161290322580645</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5376344086021505</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9969040247678018</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9690402476780186</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9442724458204335</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9969040247678018</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9938080495356038</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.9659442724458205</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.9690402476780186</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.9845201238390093</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9597523219814241</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9845201238390093</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9876160990712074</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.9690402476780186</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6304347826086957</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5869565217391305</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6739130434782609</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6304347826086957</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.7173913043478261</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2333,115 +5696,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deep4Net</t>
+          <t>Avg Ensmble</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>avg</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4946236559139785</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4731182795698925</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9247311827956989</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5268817204301075</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5268817204301075</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.4946236559139785</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5698924731182796</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4731182795698925</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.5591397849462365</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.6021505376344086</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.6236559139784946</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5161290322580645</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Train</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>avg</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>85.33933933933933</v>
-      </c>
-      <c r="E2" t="n">
-        <v>75.64432725408335</v>
-      </c>
-      <c r="F2" t="n">
-        <v>96.48516809492419</v>
-      </c>
-      <c r="G2" t="n">
-        <v>95.34534534534535</v>
-      </c>
-      <c r="H2" t="n">
-        <v>65.57884713982276</v>
-      </c>
-      <c r="I2" t="n">
-        <v>78.4166117336849</v>
-      </c>
-      <c r="J2" t="n">
-        <v>58.98088332234674</v>
-      </c>
-      <c r="K2" t="n">
-        <v>66.18603969823482</v>
-      </c>
-      <c r="L2" t="n">
-        <v>85.44495715227423</v>
-      </c>
-      <c r="M2" t="n">
-        <v>72.18662565004028</v>
-      </c>
-      <c r="N2" t="n">
-        <v>74.2934153665861</v>
-      </c>
-      <c r="O2" t="n">
-        <v>74.94074562367244</v>
-      </c>
-      <c r="P2" t="n">
-        <v>70.81974657584414</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>83.33172196586831</v>
-      </c>
-      <c r="R2" t="n">
-        <v>73.69618398886692</v>
-      </c>
-    </row>
-    <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>std</t>
+          <t>avg</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.775898321346224</v>
+        <v>0.8637770897832817</v>
       </c>
       <c r="E3" t="n">
-        <v>8.53894474514947</v>
+        <v>0.8699690402476781</v>
       </c>
       <c r="F3" t="n">
-        <v>2.944854664257522</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1.343434924255247</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>10.97315911984308</v>
+        <v>0.9102167182662538</v>
       </c>
       <c r="I3" t="n">
-        <v>10.42064659960482</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="J3" t="n">
-        <v>6.124540957836241</v>
+        <v>0.9721362229102167</v>
       </c>
       <c r="K3" t="n">
-        <v>8.927021289025443</v>
+        <v>0.9226006191950464</v>
       </c>
       <c r="L3" t="n">
-        <v>11.70183148035998</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="M3" t="n">
-        <v>9.509546533718673</v>
+        <v>0.9566563467492261</v>
       </c>
       <c r="N3" t="n">
-        <v>12.56428242879971</v>
+        <v>0.9597523219814241</v>
       </c>
       <c r="O3" t="n">
-        <v>14.61723615522784</v>
+        <v>0.9287925696594427</v>
       </c>
       <c r="P3" t="n">
-        <v>12.39919286804717</v>
+        <v>0.9845201238390093</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.729795990243382</v>
+        <v>0.9287925696594427</v>
       </c>
       <c r="R3" t="n">
-        <v>5.3159715759477</v>
+        <v>0.9102167182662538</v>
       </c>
     </row>
     <row r="4">
@@ -2456,108 +5824,54 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54.31977559607293</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="E4" t="n">
-        <v>41.57316503038803</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="F4" t="n">
-        <v>91.54978962131837</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="G4" t="n">
-        <v>87.26040205703599</v>
+        <v>0.9347826086956522</v>
       </c>
       <c r="H4" t="n">
-        <v>38.12061711079944</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="I4" t="n">
-        <v>51.92145862552595</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="J4" t="n">
-        <v>37.46376811594203</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="K4" t="n">
-        <v>43.06685366993922</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="L4" t="n">
-        <v>51.51940158952782</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="M4" t="n">
-        <v>47.82842449742871</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="N4" t="n">
-        <v>44.81299672744273</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="O4" t="n">
-        <v>42.66245909303412</v>
+        <v>0.6304347826086957</v>
       </c>
       <c r="P4" t="n">
-        <v>46.11266947171575</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="Q4" t="n">
-        <v>47.61337073398785</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="R4" t="n">
-        <v>42.87050023375409</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>std</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3.418813204777864</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5.345716366591565</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.479168747481076</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.134305949193243</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.86623390461516</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8.504475624266034</v>
-      </c>
-      <c r="J5" t="n">
-        <v>7.298795462486767</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.829573349924428</v>
-      </c>
-      <c r="L5" t="n">
-        <v>8.098272070631584</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.35593974636413</v>
-      </c>
-      <c r="N5" t="n">
-        <v>7.268036067652654</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6.336078723364192</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.823545321897829</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.098399213094644</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.812958436977647</v>
+        <v>0.5434782608695652</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
